--- a/212-corriger-interopsanteorg/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/212-corriger-interopsanteorg/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11058" uniqueCount="979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11058" uniqueCount="978">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T16:13:56+00:00</t>
+    <t>2024-07-01T16:18:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1212,7 +1212,7 @@
   </si>
   <si>
     <t>Type d’identifiant national de la personne physique (typeIdNat_PP),
-Les codes ADELI, RPPS et IDNPS proviennent du system  http://interopsante.org/fhir/CodeSystem/fr-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
+Les codes ADELI, RPPS et IDNPS proviennent du system  https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
   </si>
   <si>
     <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
@@ -1535,10 +1535,6 @@
   </si>
   <si>
     <t>Practitioner.identifier:idNatPs.type</t>
-  </si>
-  <si>
-    <t>Type d’identifiant national de la personne physique (typeIdNat_PP),
-Les codes ADELI, RPPS et IDNPS proviennent du system  https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -1691,7 +1687,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/fhir/CodeSystem/fr-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="INTRN"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -16832,7 +16828,7 @@
         <v>233</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>491</v>
+        <v>384</v>
       </c>
       <c r="M116" t="s" s="2">
         <v>385</v>
@@ -16851,7 +16847,7 @@
         <v>78</v>
       </c>
       <c r="S116" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="T116" t="s" s="2">
         <v>78</v>
@@ -16869,10 +16865,10 @@
         <v>158</v>
       </c>
       <c r="Y116" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="Z116" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>78</v>
@@ -16922,7 +16918,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>449</v>
@@ -16954,7 +16950,7 @@
         <v>450</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="N117" t="s" s="2">
         <v>452</v>
@@ -16970,7 +16966,7 @@
         <v>78</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>454</v>
@@ -17041,7 +17037,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>459</v>
@@ -17070,7 +17066,7 @@
         <v>104</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="M118" t="s" s="2">
         <v>461</v>
@@ -17158,7 +17154,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>468</v>
@@ -17273,7 +17269,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>475</v>
@@ -17390,13 +17386,13 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>361</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>78</v>
@@ -17421,7 +17417,7 @@
         <v>362</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="M121" t="s" s="2">
         <v>364</v>
@@ -17509,7 +17505,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>372</v>
@@ -17624,7 +17620,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>373</v>
@@ -17741,7 +17737,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>374</v>
@@ -17860,7 +17856,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>383</v>
@@ -17889,7 +17885,7 @@
         <v>233</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="M125" t="s" s="2">
         <v>385</v>
@@ -17908,7 +17904,7 @@
         <v>78</v>
       </c>
       <c r="S125" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="T125" t="s" s="2">
         <v>78</v>
@@ -17926,10 +17922,10 @@
         <v>158</v>
       </c>
       <c r="Y125" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="Z125" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>78</v>
@@ -17979,7 +17975,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>449</v>
@@ -18011,7 +18007,7 @@
         <v>450</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="N126" t="s" s="2">
         <v>452</v>
@@ -18027,7 +18023,7 @@
         <v>78</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>454</v>
@@ -18098,7 +18094,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>459</v>
@@ -18215,7 +18211,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>468</v>
@@ -18330,7 +18326,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>475</v>
@@ -18447,13 +18443,13 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>361</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>78</v>
@@ -18478,7 +18474,7 @@
         <v>362</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="M130" t="s" s="2">
         <v>364</v>
@@ -18566,7 +18562,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>372</v>
@@ -18681,7 +18677,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>373</v>
@@ -18798,7 +18794,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>374</v>
@@ -18917,7 +18913,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>383</v>
@@ -18946,7 +18942,7 @@
         <v>233</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="M134" t="s" s="2">
         <v>385</v>
@@ -18965,7 +18961,7 @@
         <v>78</v>
       </c>
       <c r="S134" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="T134" t="s" s="2">
         <v>78</v>
@@ -18983,10 +18979,10 @@
         <v>158</v>
       </c>
       <c r="Y134" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="Z134" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="Z134" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>78</v>
@@ -19036,7 +19032,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>449</v>
@@ -19068,7 +19064,7 @@
         <v>450</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="N135" t="s" s="2">
         <v>452</v>
@@ -19084,7 +19080,7 @@
         <v>78</v>
       </c>
       <c r="S135" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="T135" t="s" s="2">
         <v>454</v>
@@ -19155,7 +19151,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>459</v>
@@ -19272,7 +19268,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>468</v>
@@ -19387,7 +19383,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>475</v>
@@ -19504,13 +19500,13 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>361</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D139" t="s" s="2">
         <v>78</v>
@@ -19535,7 +19531,7 @@
         <v>362</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="M139" t="s" s="2">
         <v>364</v>
@@ -19623,7 +19619,7 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>372</v>
@@ -19738,7 +19734,7 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>373</v>
@@ -19855,7 +19851,7 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>374</v>
@@ -19974,7 +19970,7 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>383</v>
@@ -20003,7 +19999,7 @@
         <v>233</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="M143" t="s" s="2">
         <v>385</v>
@@ -20022,7 +20018,7 @@
         <v>78</v>
       </c>
       <c r="S143" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="T143" t="s" s="2">
         <v>78</v>
@@ -20040,10 +20036,10 @@
         <v>158</v>
       </c>
       <c r="Y143" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="Z143" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="Z143" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>78</v>
@@ -20093,7 +20089,7 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>449</v>
@@ -20122,10 +20118,10 @@
         <v>137</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>452</v>
@@ -20160,7 +20156,7 @@
       </c>
       <c r="Y144" s="2"/>
       <c r="Z144" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>78</v>
@@ -20210,7 +20206,7 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>459</v>
@@ -20239,7 +20235,7 @@
         <v>104</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="M145" t="s" s="2">
         <v>461</v>
@@ -20327,7 +20323,7 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>468</v>
@@ -20362,7 +20358,7 @@
         <v>470</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -20424,7 +20420,7 @@
         <v>209</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AK146" t="s" s="2">
         <v>78</v>
@@ -20444,7 +20440,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>475</v>
@@ -20541,7 +20537,7 @@
         <v>209</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>78</v>
@@ -20561,10 +20557,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20590,23 +20586,23 @@
         <v>297</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M148" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="M148" t="s" s="2">
+      <c r="N148" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="N148" t="s" s="2">
+      <c r="O148" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="O148" t="s" s="2">
+      <c r="P148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q148" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="P148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q148" t="s" s="2">
-        <v>552</v>
-      </c>
       <c r="R148" t="s" s="2">
         <v>78</v>
       </c>
@@ -20650,7 +20646,7 @@
         <v>78</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -20671,21 +20667,21 @@
         <v>78</v>
       </c>
       <c r="AM148" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AN148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO148" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="AN148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO148" t="s" s="2">
-        <v>554</v>
       </c>
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20708,19 +20704,19 @@
         <v>78</v>
       </c>
       <c r="K149" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="L149" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="L149" t="s" s="2">
+      <c r="M149" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="M149" t="s" s="2">
+      <c r="N149" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="N149" t="s" s="2">
+      <c r="O149" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>78</v>
@@ -20769,7 +20765,7 @@
         <v>78</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20787,13 +20783,13 @@
         <v>78</v>
       </c>
       <c r="AL149" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AM149" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="AM149" t="s" s="2">
+      <c r="AN149" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="AN149" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>78</v>
@@ -20801,10 +20797,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20916,10 +20912,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21033,13 +21029,13 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="C152" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="B152" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="C152" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>78</v>
@@ -21061,13 +21057,13 @@
         <v>78</v>
       </c>
       <c r="K152" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="L152" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="L152" t="s" s="2">
+      <c r="M152" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -21150,10 +21146,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21179,16 +21175,16 @@
         <v>176</v>
       </c>
       <c r="L153" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M153" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="M153" t="s" s="2">
+      <c r="N153" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="N153" t="s" s="2">
+      <c r="O153" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>78</v>
@@ -21217,25 +21213,25 @@
       </c>
       <c r="Y153" s="2"/>
       <c r="Z153" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AA153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF153" t="s" s="2">
         <v>576</v>
-      </c>
-      <c r="AA153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE153" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF153" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
@@ -21253,13 +21249,13 @@
         <v>78</v>
       </c>
       <c r="AL153" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AM153" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="AM153" t="s" s="2">
+      <c r="AN153" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="AN153" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>78</v>
@@ -21267,10 +21263,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21296,16 +21292,16 @@
         <v>104</v>
       </c>
       <c r="L154" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M154" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="M154" t="s" s="2">
+      <c r="N154" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="N154" t="s" s="2">
+      <c r="O154" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>78</v>
@@ -21354,7 +21350,7 @@
         <v>78</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -21372,10 +21368,10 @@
         <v>78</v>
       </c>
       <c r="AL154" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AM154" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="AM154" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>78</v>
@@ -21386,14 +21382,14 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
@@ -21415,13 +21411,13 @@
         <v>104</v>
       </c>
       <c r="L155" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M155" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="M155" t="s" s="2">
+      <c r="N155" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -21471,7 +21467,7 @@
         <v>78</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -21489,13 +21485,13 @@
         <v>78</v>
       </c>
       <c r="AL155" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AM155" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="AM155" t="s" s="2">
+      <c r="AN155" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="AN155" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>78</v>
@@ -21503,14 +21499,14 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -21532,13 +21528,13 @@
         <v>104</v>
       </c>
       <c r="L156" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M156" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="M156" t="s" s="2">
+      <c r="N156" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -21588,7 +21584,7 @@
         <v>78</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -21606,13 +21602,13 @@
         <v>78</v>
       </c>
       <c r="AL156" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AM156" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="AM156" t="s" s="2">
+      <c r="AN156" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="AN156" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>78</v>
@@ -21620,10 +21616,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21649,10 +21645,10 @@
         <v>104</v>
       </c>
       <c r="L157" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M157" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="M157" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -21682,28 +21678,28 @@
         <v>158</v>
       </c>
       <c r="Y157" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="Z157" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="Z157" t="s" s="2">
+      <c r="AA157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF157" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AA157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE157" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF157" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -21721,13 +21717,13 @@
         <v>78</v>
       </c>
       <c r="AL157" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AM157" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="AM157" t="s" s="2">
+      <c r="AN157" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="AN157" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>78</v>
@@ -21735,10 +21731,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21764,10 +21760,10 @@
         <v>104</v>
       </c>
       <c r="L158" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="M158" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -21797,28 +21793,28 @@
         <v>158</v>
       </c>
       <c r="Y158" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="Z158" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="Z158" t="s" s="2">
+      <c r="AA158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF158" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="AA158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE158" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF158" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -21836,10 +21832,10 @@
         <v>78</v>
       </c>
       <c r="AL158" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AM158" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="AM158" t="s" s="2">
-        <v>623</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>78</v>
@@ -21850,10 +21846,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21879,14 +21875,14 @@
         <v>253</v>
       </c>
       <c r="L159" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="M159" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="M159" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>78</v>
@@ -21935,7 +21931,7 @@
         <v>78</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -21953,10 +21949,10 @@
         <v>78</v>
       </c>
       <c r="AL159" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AM159" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="AM159" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>474</v>
@@ -21967,10 +21963,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21993,19 +21989,19 @@
         <v>78</v>
       </c>
       <c r="K160" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="L160" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="L160" t="s" s="2">
+      <c r="M160" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="M160" t="s" s="2">
+      <c r="N160" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="N160" t="s" s="2">
+      <c r="O160" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="O160" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>78</v>
@@ -22042,17 +22038,17 @@
         <v>78</v>
       </c>
       <c r="AB160" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="AC160" s="2"/>
       <c r="AD160" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE160" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -22064,19 +22060,19 @@
         <v>209</v>
       </c>
       <c r="AJ160" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AK160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL160" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="AK160" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL160" t="s" s="2">
+      <c r="AM160" t="s" s="2">
         <v>640</v>
       </c>
-      <c r="AM160" t="s" s="2">
+      <c r="AN160" t="s" s="2">
         <v>641</v>
-      </c>
-      <c r="AN160" t="s" s="2">
-        <v>642</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>78</v>
@@ -22084,13 +22080,13 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="C161" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="B161" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="C161" t="s" s="2">
-        <v>644</v>
       </c>
       <c r="D161" t="s" s="2">
         <v>78</v>
@@ -22112,19 +22108,19 @@
         <v>78</v>
       </c>
       <c r="K161" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="L161" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="L161" t="s" s="2">
-        <v>646</v>
-      </c>
       <c r="M161" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="N161" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="N161" t="s" s="2">
+      <c r="O161" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="O161" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>78</v>
@@ -22173,7 +22169,7 @@
         <v>78</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
@@ -22185,19 +22181,19 @@
         <v>209</v>
       </c>
       <c r="AJ161" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AK161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL161" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="AK161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL161" t="s" s="2">
+      <c r="AM161" t="s" s="2">
         <v>640</v>
       </c>
-      <c r="AM161" t="s" s="2">
+      <c r="AN161" t="s" s="2">
         <v>641</v>
-      </c>
-      <c r="AN161" t="s" s="2">
-        <v>642</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>78</v>
@@ -22205,10 +22201,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="B162" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="B162" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22320,10 +22316,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="B163" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="B163" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22437,13 +22433,13 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="B164" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="C164" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="B164" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="C164" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="D164" t="s" s="2">
         <v>78</v>
@@ -22465,13 +22461,13 @@
         <v>78</v>
       </c>
       <c r="K164" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="L164" t="s" s="2">
         <v>653</v>
       </c>
-      <c r="L164" t="s" s="2">
+      <c r="M164" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="M164" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -22554,10 +22550,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="B165" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="B165" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22669,10 +22665,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="B166" t="s" s="2">
         <v>658</v>
-      </c>
-      <c r="B166" t="s" s="2">
-        <v>659</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22784,10 +22780,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="B167" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="B167" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22827,7 +22823,7 @@
       </c>
       <c r="Q167" s="2"/>
       <c r="R167" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="S167" t="s" s="2">
         <v>78</v>
@@ -22901,10 +22897,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="B168" t="s" s="2">
         <v>663</v>
-      </c>
-      <c r="B168" t="s" s="2">
-        <v>664</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22945,7 +22941,7 @@
         <v>78</v>
       </c>
       <c r="S168" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="T168" t="s" s="2">
         <v>78</v>
@@ -22964,7 +22960,7 @@
       </c>
       <c r="Y168" s="2"/>
       <c r="Z168" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>78</v>
@@ -23014,13 +23010,13 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B169" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="C169" t="s" s="2">
         <v>667</v>
-      </c>
-      <c r="B169" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="C169" t="s" s="2">
-        <v>668</v>
       </c>
       <c r="D169" t="s" s="2">
         <v>78</v>
@@ -23042,13 +23038,13 @@
         <v>78</v>
       </c>
       <c r="K169" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="L169" t="s" s="2">
         <v>669</v>
       </c>
-      <c r="L169" t="s" s="2">
+      <c r="M169" t="s" s="2">
         <v>670</v>
-      </c>
-      <c r="M169" t="s" s="2">
-        <v>671</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -23131,10 +23127,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23246,10 +23242,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23363,10 +23359,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C172" t="s" s="2">
         <v>312</v>
@@ -23394,7 +23390,7 @@
         <v>111</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="M172" t="s" s="2">
         <v>202</v>
@@ -23480,10 +23476,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="B173" t="s" s="2">
         <v>676</v>
-      </c>
-      <c r="B173" t="s" s="2">
-        <v>677</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23595,10 +23591,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="B174" t="s" s="2">
         <v>678</v>
-      </c>
-      <c r="B174" t="s" s="2">
-        <v>679</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23710,10 +23706,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="B175" t="s" s="2">
         <v>680</v>
-      </c>
-      <c r="B175" t="s" s="2">
-        <v>681</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23827,10 +23823,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="B176" t="s" s="2">
         <v>682</v>
-      </c>
-      <c r="B176" t="s" s="2">
-        <v>683</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23890,7 +23886,7 @@
       </c>
       <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>78</v>
@@ -23940,13 +23936,13 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="B177" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="C177" t="s" s="2">
         <v>685</v>
-      </c>
-      <c r="B177" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="C177" t="s" s="2">
-        <v>686</v>
       </c>
       <c r="D177" t="s" s="2">
         <v>78</v>
@@ -23971,7 +23967,7 @@
         <v>111</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="M177" t="s" s="2">
         <v>202</v>
@@ -24057,10 +24053,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24172,10 +24168,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24287,10 +24283,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24330,7 +24326,7 @@
       </c>
       <c r="Q180" s="2"/>
       <c r="R180" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="S180" t="s" s="2">
         <v>78</v>
@@ -24404,10 +24400,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24519,13 +24515,13 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="B182" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="C182" t="s" s="2">
         <v>692</v>
-      </c>
-      <c r="B182" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="C182" t="s" s="2">
-        <v>693</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>78</v>
@@ -24636,10 +24632,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24751,10 +24747,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24866,10 +24862,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24909,7 +24905,7 @@
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>78</v>
@@ -24983,10 +24979,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25098,13 +25094,13 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="B187" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="C187" t="s" s="2">
         <v>698</v>
-      </c>
-      <c r="B187" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="C187" t="s" s="2">
-        <v>699</v>
       </c>
       <c r="D187" t="s" s="2">
         <v>78</v>
@@ -25129,7 +25125,7 @@
         <v>111</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M187" t="s" s="2">
         <v>202</v>
@@ -25215,10 +25211,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25330,10 +25326,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25445,10 +25441,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25488,7 +25484,7 @@
       </c>
       <c r="Q190" s="2"/>
       <c r="R190" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="S190" t="s" s="2">
         <v>78</v>
@@ -25562,10 +25558,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25677,13 +25673,13 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="B192" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="C192" t="s" s="2">
         <v>705</v>
-      </c>
-      <c r="B192" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="C192" t="s" s="2">
-        <v>706</v>
       </c>
       <c r="D192" t="s" s="2">
         <v>78</v>
@@ -25794,10 +25790,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25909,10 +25905,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26024,10 +26020,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26067,7 +26063,7 @@
       </c>
       <c r="Q195" s="2"/>
       <c r="R195" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="S195" t="s" s="2">
         <v>78</v>
@@ -26141,10 +26137,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26256,13 +26252,13 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="B197" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="C197" t="s" s="2">
         <v>711</v>
-      </c>
-      <c r="B197" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="C197" t="s" s="2">
-        <v>712</v>
       </c>
       <c r="D197" t="s" s="2">
         <v>78</v>
@@ -26287,7 +26283,7 @@
         <v>111</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="M197" t="s" s="2">
         <v>202</v>
@@ -26373,10 +26369,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26488,10 +26484,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26603,10 +26599,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26646,7 +26642,7 @@
       </c>
       <c r="Q200" s="2"/>
       <c r="R200" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="S200" t="s" s="2">
         <v>78</v>
@@ -26720,10 +26716,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26835,13 +26831,13 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="B202" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="C202" t="s" s="2">
         <v>718</v>
-      </c>
-      <c r="B202" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="C202" t="s" s="2">
-        <v>719</v>
       </c>
       <c r="D202" t="s" s="2">
         <v>78</v>
@@ -26866,7 +26862,7 @@
         <v>111</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="M202" t="s" s="2">
         <v>202</v>
@@ -26952,10 +26948,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27067,10 +27063,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -27182,10 +27178,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27225,7 +27221,7 @@
       </c>
       <c r="Q205" s="2"/>
       <c r="R205" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="S205" t="s" s="2">
         <v>78</v>
@@ -27299,10 +27295,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27414,10 +27410,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27457,7 +27453,7 @@
       </c>
       <c r="Q207" s="2"/>
       <c r="R207" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="S207" t="s" s="2">
         <v>78</v>
@@ -27531,10 +27527,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27646,10 +27642,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="B209" t="s" s="2">
         <v>728</v>
-      </c>
-      <c r="B209" t="s" s="2">
-        <v>729</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27675,10 +27671,10 @@
         <v>176</v>
       </c>
       <c r="L209" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="M209" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="M209" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" s="2"/>
@@ -27690,7 +27686,7 @@
         <v>78</v>
       </c>
       <c r="S209" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="T209" t="s" s="2">
         <v>78</v>
@@ -27708,37 +27704,37 @@
         <v>236</v>
       </c>
       <c r="Y209" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="Z209" t="s" s="2">
         <v>733</v>
       </c>
-      <c r="Z209" t="s" s="2">
+      <c r="AA209" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB209" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC209" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD209" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE209" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF209" t="s" s="2">
         <v>734</v>
       </c>
-      <c r="AA209" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB209" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC209" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD209" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE209" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF209" t="s" s="2">
+      <c r="AG209" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH209" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI209" t="s" s="2">
         <v>735</v>
-      </c>
-      <c r="AG209" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH209" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI209" t="s" s="2">
-        <v>736</v>
       </c>
       <c r="AJ209" t="s" s="2">
         <v>102</v>
@@ -27747,13 +27743,13 @@
         <v>78</v>
       </c>
       <c r="AL209" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="AM209" t="s" s="2">
         <v>737</v>
       </c>
-      <c r="AM209" t="s" s="2">
+      <c r="AN209" t="s" s="2">
         <v>738</v>
-      </c>
-      <c r="AN209" t="s" s="2">
-        <v>739</v>
       </c>
       <c r="AO209" t="s" s="2">
         <v>78</v>
@@ -27761,10 +27757,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="B210" t="s" s="2">
         <v>740</v>
-      </c>
-      <c r="B210" t="s" s="2">
-        <v>741</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -27790,16 +27786,16 @@
         <v>104</v>
       </c>
       <c r="L210" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="M210" t="s" s="2">
         <v>742</v>
       </c>
-      <c r="M210" t="s" s="2">
+      <c r="N210" t="s" s="2">
         <v>743</v>
       </c>
-      <c r="N210" t="s" s="2">
+      <c r="O210" t="s" s="2">
         <v>744</v>
-      </c>
-      <c r="O210" t="s" s="2">
-        <v>745</v>
       </c>
       <c r="P210" t="s" s="2">
         <v>78</v>
@@ -27848,7 +27844,7 @@
         <v>78</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>79</v>
@@ -27866,10 +27862,10 @@
         <v>78</v>
       </c>
       <c r="AL210" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="AM210" t="s" s="2">
         <v>747</v>
-      </c>
-      <c r="AM210" t="s" s="2">
-        <v>748</v>
       </c>
       <c r="AN210" t="s" s="2">
         <v>467</v>
@@ -27880,10 +27876,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="B211" t="s" s="2">
         <v>749</v>
-      </c>
-      <c r="B211" t="s" s="2">
-        <v>750</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -27909,16 +27905,16 @@
         <v>176</v>
       </c>
       <c r="L211" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="M211" t="s" s="2">
         <v>751</v>
       </c>
-      <c r="M211" t="s" s="2">
+      <c r="N211" t="s" s="2">
         <v>752</v>
       </c>
-      <c r="N211" t="s" s="2">
+      <c r="O211" t="s" s="2">
         <v>753</v>
-      </c>
-      <c r="O211" t="s" s="2">
-        <v>754</v>
       </c>
       <c r="P211" t="s" s="2">
         <v>78</v>
@@ -27946,28 +27942,28 @@
         <v>236</v>
       </c>
       <c r="Y211" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="Z211" t="s" s="2">
         <v>755</v>
       </c>
-      <c r="Z211" t="s" s="2">
+      <c r="AA211" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB211" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC211" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD211" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE211" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF211" t="s" s="2">
         <v>756</v>
-      </c>
-      <c r="AA211" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB211" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC211" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD211" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE211" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF211" t="s" s="2">
-        <v>757</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>79</v>
@@ -27985,13 +27981,13 @@
         <v>78</v>
       </c>
       <c r="AL211" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="AM211" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AN211" t="s" s="2">
         <v>758</v>
-      </c>
-      <c r="AM211" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="AN211" t="s" s="2">
-        <v>759</v>
       </c>
       <c r="AO211" t="s" s="2">
         <v>78</v>
@@ -27999,10 +27995,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="B212" t="s" s="2">
         <v>760</v>
-      </c>
-      <c r="B212" t="s" s="2">
-        <v>761</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28025,16 +28021,16 @@
         <v>91</v>
       </c>
       <c r="K212" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="L212" t="s" s="2">
         <v>762</v>
       </c>
-      <c r="L212" t="s" s="2">
+      <c r="M212" t="s" s="2">
         <v>763</v>
       </c>
-      <c r="M212" t="s" s="2">
+      <c r="N212" t="s" s="2">
         <v>764</v>
-      </c>
-      <c r="N212" t="s" s="2">
-        <v>765</v>
       </c>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
@@ -28084,7 +28080,7 @@
         <v>78</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>79</v>
@@ -28116,10 +28112,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="B213" t="s" s="2">
         <v>767</v>
-      </c>
-      <c r="B213" t="s" s="2">
-        <v>768</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28145,10 +28141,10 @@
         <v>253</v>
       </c>
       <c r="L213" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="M213" t="s" s="2">
         <v>769</v>
-      </c>
-      <c r="M213" t="s" s="2">
-        <v>770</v>
       </c>
       <c r="N213" s="2"/>
       <c r="O213" s="2"/>
@@ -28199,7 +28195,7 @@
         <v>78</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>79</v>
@@ -28220,7 +28216,7 @@
         <v>199</v>
       </c>
       <c r="AM213" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AN213" t="s" s="2">
         <v>474</v>
@@ -28231,10 +28227,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28257,19 +28253,19 @@
         <v>78</v>
       </c>
       <c r="K214" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="L214" t="s" s="2">
         <v>773</v>
       </c>
-      <c r="L214" t="s" s="2">
+      <c r="M214" t="s" s="2">
         <v>774</v>
       </c>
-      <c r="M214" t="s" s="2">
+      <c r="N214" t="s" s="2">
         <v>775</v>
       </c>
-      <c r="N214" t="s" s="2">
+      <c r="O214" t="s" s="2">
         <v>776</v>
-      </c>
-      <c r="O214" t="s" s="2">
-        <v>777</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>78</v>
@@ -28318,7 +28314,7 @@
         <v>78</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>79</v>
@@ -28336,13 +28332,13 @@
         <v>78</v>
       </c>
       <c r="AL214" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="AM214" t="s" s="2">
         <v>778</v>
       </c>
-      <c r="AM214" t="s" s="2">
+      <c r="AN214" t="s" s="2">
         <v>779</v>
-      </c>
-      <c r="AN214" t="s" s="2">
-        <v>780</v>
       </c>
       <c r="AO214" t="s" s="2">
         <v>78</v>
@@ -28350,10 +28346,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28379,14 +28375,14 @@
         <v>176</v>
       </c>
       <c r="L215" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="M215" t="s" s="2">
         <v>782</v>
-      </c>
-      <c r="M215" t="s" s="2">
-        <v>783</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>78</v>
@@ -28414,11 +28410,11 @@
         <v>236</v>
       </c>
       <c r="Y215" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="Z215" t="s" s="2">
         <v>785</v>
       </c>
-      <c r="Z215" t="s" s="2">
-        <v>786</v>
-      </c>
       <c r="AA215" t="s" s="2">
         <v>78</v>
       </c>
@@ -28435,7 +28431,7 @@
         <v>78</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>79</v>
@@ -28453,13 +28449,13 @@
         <v>78</v>
       </c>
       <c r="AL215" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="AM215" t="s" s="2">
         <v>787</v>
       </c>
-      <c r="AM215" t="s" s="2">
+      <c r="AN215" t="s" s="2">
         <v>788</v>
-      </c>
-      <c r="AN215" t="s" s="2">
-        <v>789</v>
       </c>
       <c r="AO215" t="s" s="2">
         <v>78</v>
@@ -28467,10 +28463,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -28493,17 +28489,17 @@
         <v>91</v>
       </c>
       <c r="K216" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="L216" t="s" s="2">
         <v>791</v>
       </c>
-      <c r="L216" t="s" s="2">
+      <c r="M216" t="s" s="2">
         <v>792</v>
-      </c>
-      <c r="M216" t="s" s="2">
-        <v>793</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" t="s" s="2">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="P216" t="s" s="2">
         <v>78</v>
@@ -28552,7 +28548,7 @@
         <v>78</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>79</v>
@@ -28570,13 +28566,13 @@
         <v>78</v>
       </c>
       <c r="AL216" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="AM216" t="s" s="2">
         <v>795</v>
       </c>
-      <c r="AM216" t="s" s="2">
+      <c r="AN216" t="s" s="2">
         <v>796</v>
-      </c>
-      <c r="AN216" t="s" s="2">
-        <v>797</v>
       </c>
       <c r="AO216" t="s" s="2">
         <v>78</v>
@@ -28584,10 +28580,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28610,17 +28606,17 @@
         <v>78</v>
       </c>
       <c r="K217" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="L217" t="s" s="2">
         <v>799</v>
       </c>
-      <c r="L217" t="s" s="2">
+      <c r="M217" t="s" s="2">
         <v>800</v>
-      </c>
-      <c r="M217" t="s" s="2">
-        <v>801</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>78</v>
@@ -28669,7 +28665,7 @@
         <v>78</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>79</v>
@@ -28690,10 +28686,10 @@
         <v>78</v>
       </c>
       <c r="AM217" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="AN217" t="s" s="2">
         <v>803</v>
-      </c>
-      <c r="AN217" t="s" s="2">
-        <v>804</v>
       </c>
       <c r="AO217" t="s" s="2">
         <v>78</v>
@@ -28701,10 +28697,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -28727,13 +28723,13 @@
         <v>78</v>
       </c>
       <c r="K218" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="L218" t="s" s="2">
         <v>806</v>
       </c>
-      <c r="L218" t="s" s="2">
+      <c r="M218" t="s" s="2">
         <v>807</v>
-      </c>
-      <c r="M218" t="s" s="2">
-        <v>808</v>
       </c>
       <c r="N218" s="2"/>
       <c r="O218" s="2"/>
@@ -28772,7 +28768,7 @@
         <v>78</v>
       </c>
       <c r="AB218" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="AC218" s="2"/>
       <c r="AD218" t="s" s="2">
@@ -28782,7 +28778,7 @@
         <v>117</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>79</v>
@@ -28800,13 +28796,13 @@
         <v>78</v>
       </c>
       <c r="AL218" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="AM218" t="s" s="2">
         <v>810</v>
       </c>
-      <c r="AM218" t="s" s="2">
+      <c r="AN218" t="s" s="2">
         <v>811</v>
-      </c>
-      <c r="AN218" t="s" s="2">
-        <v>812</v>
       </c>
       <c r="AO218" t="s" s="2">
         <v>78</v>
@@ -28814,10 +28810,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -28929,10 +28925,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29046,14 +29042,14 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E221" s="2"/>
       <c r="F221" t="s" s="2">
@@ -29075,10 +29071,10 @@
         <v>111</v>
       </c>
       <c r="L221" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="M221" t="s" s="2">
         <v>817</v>
-      </c>
-      <c r="M221" t="s" s="2">
-        <v>818</v>
       </c>
       <c r="N221" t="s" s="2">
         <v>114</v>
@@ -29133,7 +29129,7 @@
         <v>78</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>79</v>
@@ -29165,10 +29161,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -29194,14 +29190,14 @@
         <v>362</v>
       </c>
       <c r="L222" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="M222" t="s" s="2">
         <v>821</v>
-      </c>
-      <c r="M222" t="s" s="2">
-        <v>822</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>78</v>
@@ -29250,7 +29246,7 @@
         <v>78</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>79</v>
@@ -29271,7 +29267,7 @@
         <v>78</v>
       </c>
       <c r="AM222" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="AN222" t="s" s="2">
         <v>78</v>
@@ -29282,10 +29278,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -29311,10 +29307,10 @@
         <v>233</v>
       </c>
       <c r="L223" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="M223" t="s" s="2">
         <v>826</v>
-      </c>
-      <c r="M223" t="s" s="2">
-        <v>827</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" s="2"/>
@@ -29345,7 +29341,7 @@
       </c>
       <c r="Y223" s="2"/>
       <c r="Z223" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="AA223" t="s" s="2">
         <v>78</v>
@@ -29363,7 +29359,7 @@
         <v>78</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>90</v>
@@ -29384,10 +29380,10 @@
         <v>78</v>
       </c>
       <c r="AM223" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="AN223" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="AO223" t="s" s="2">
         <v>78</v>
@@ -29395,10 +29391,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29424,14 +29420,14 @@
         <v>253</v>
       </c>
       <c r="L224" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="M224" t="s" s="2">
         <v>831</v>
-      </c>
-      <c r="M224" t="s" s="2">
-        <v>832</v>
       </c>
       <c r="N224" s="2"/>
       <c r="O224" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="P224" t="s" s="2">
         <v>78</v>
@@ -29480,7 +29476,7 @@
         <v>78</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>79</v>
@@ -29501,10 +29497,10 @@
         <v>78</v>
       </c>
       <c r="AM224" t="s" s="2">
+        <v>833</v>
+      </c>
+      <c r="AN224" t="s" s="2">
         <v>834</v>
-      </c>
-      <c r="AN224" t="s" s="2">
-        <v>835</v>
       </c>
       <c r="AO224" t="s" s="2">
         <v>78</v>
@@ -29512,10 +29508,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -29541,10 +29537,10 @@
         <v>476</v>
       </c>
       <c r="L225" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="M225" t="s" s="2">
         <v>837</v>
-      </c>
-      <c r="M225" t="s" s="2">
-        <v>838</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
@@ -29595,7 +29591,7 @@
         <v>78</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>79</v>
@@ -29616,7 +29612,7 @@
         <v>78</v>
       </c>
       <c r="AM225" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="AN225" t="s" s="2">
         <v>78</v>
@@ -29627,13 +29623,13 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="B226" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="C226" t="s" s="2">
         <v>840</v>
-      </c>
-      <c r="B226" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="C226" t="s" s="2">
-        <v>841</v>
       </c>
       <c r="D226" t="s" s="2">
         <v>78</v>
@@ -29655,13 +29651,13 @@
         <v>78</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="N226" s="2"/>
       <c r="O226" s="2"/>
@@ -29712,7 +29708,7 @@
         <v>78</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>79</v>
@@ -29730,13 +29726,13 @@
         <v>78</v>
       </c>
       <c r="AL226" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="AM226" t="s" s="2">
         <v>810</v>
       </c>
-      <c r="AM226" t="s" s="2">
+      <c r="AN226" t="s" s="2">
         <v>811</v>
-      </c>
-      <c r="AN226" t="s" s="2">
-        <v>812</v>
       </c>
       <c r="AO226" t="s" s="2">
         <v>78</v>
@@ -29744,10 +29740,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -29859,10 +29855,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -29972,13 +29968,13 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
+        <v>844</v>
+      </c>
+      <c r="B229" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="C229" t="s" s="2">
         <v>845</v>
-      </c>
-      <c r="B229" t="s" s="2">
-        <v>814</v>
-      </c>
-      <c r="C229" t="s" s="2">
-        <v>846</v>
       </c>
       <c r="D229" t="s" s="2">
         <v>78</v>
@@ -30000,13 +29996,13 @@
         <v>78</v>
       </c>
       <c r="K229" t="s" s="2">
+        <v>846</v>
+      </c>
+      <c r="L229" t="s" s="2">
         <v>847</v>
       </c>
-      <c r="L229" t="s" s="2">
+      <c r="M229" t="s" s="2">
         <v>848</v>
-      </c>
-      <c r="M229" t="s" s="2">
-        <v>849</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -30089,10 +30085,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
+        <v>849</v>
+      </c>
+      <c r="B230" t="s" s="2">
         <v>850</v>
-      </c>
-      <c r="B230" t="s" s="2">
-        <v>851</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -30204,10 +30200,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
+        <v>851</v>
+      </c>
+      <c r="B231" t="s" s="2">
         <v>852</v>
-      </c>
-      <c r="B231" t="s" s="2">
-        <v>853</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -30321,13 +30317,13 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
+        <v>853</v>
+      </c>
+      <c r="B232" t="s" s="2">
+        <v>852</v>
+      </c>
+      <c r="C232" t="s" s="2">
         <v>854</v>
-      </c>
-      <c r="B232" t="s" s="2">
-        <v>853</v>
-      </c>
-      <c r="C232" t="s" s="2">
-        <v>855</v>
       </c>
       <c r="D232" t="s" s="2">
         <v>78</v>
@@ -30438,10 +30434,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
+        <v>855</v>
+      </c>
+      <c r="B233" t="s" s="2">
         <v>856</v>
-      </c>
-      <c r="B233" t="s" s="2">
-        <v>857</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -30553,10 +30549,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
+        <v>857</v>
+      </c>
+      <c r="B234" t="s" s="2">
         <v>858</v>
-      </c>
-      <c r="B234" t="s" s="2">
-        <v>859</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -30668,10 +30664,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
+        <v>859</v>
+      </c>
+      <c r="B235" t="s" s="2">
         <v>860</v>
-      </c>
-      <c r="B235" t="s" s="2">
-        <v>861</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -30711,7 +30707,7 @@
       </c>
       <c r="Q235" s="2"/>
       <c r="R235" t="s" s="2">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="S235" t="s" s="2">
         <v>78</v>
@@ -30785,10 +30781,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
+        <v>861</v>
+      </c>
+      <c r="B236" t="s" s="2">
         <v>862</v>
-      </c>
-      <c r="B236" t="s" s="2">
-        <v>863</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -30848,7 +30844,7 @@
       </c>
       <c r="Y236" s="2"/>
       <c r="Z236" t="s" s="2">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="AA236" t="s" s="2">
         <v>78</v>
@@ -30898,13 +30894,13 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
+        <v>864</v>
+      </c>
+      <c r="B237" t="s" s="2">
+        <v>852</v>
+      </c>
+      <c r="C237" t="s" s="2">
         <v>865</v>
-      </c>
-      <c r="B237" t="s" s="2">
-        <v>853</v>
-      </c>
-      <c r="C237" t="s" s="2">
-        <v>866</v>
       </c>
       <c r="D237" t="s" s="2">
         <v>78</v>
@@ -31015,10 +31011,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -31130,10 +31126,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -31245,10 +31241,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -31288,7 +31284,7 @@
       </c>
       <c r="Q240" s="2"/>
       <c r="R240" t="s" s="2">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="S240" t="s" s="2">
         <v>78</v>
@@ -31362,10 +31358,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -31425,7 +31421,7 @@
       </c>
       <c r="Y241" s="2"/>
       <c r="Z241" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="AA241" t="s" s="2">
         <v>78</v>
@@ -31475,13 +31471,13 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
+        <v>871</v>
+      </c>
+      <c r="B242" t="s" s="2">
+        <v>852</v>
+      </c>
+      <c r="C242" t="s" s="2">
         <v>872</v>
-      </c>
-      <c r="B242" t="s" s="2">
-        <v>853</v>
-      </c>
-      <c r="C242" t="s" s="2">
-        <v>873</v>
       </c>
       <c r="D242" t="s" s="2">
         <v>78</v>
@@ -31592,10 +31588,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -31707,10 +31703,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -31822,10 +31818,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -31865,7 +31861,7 @@
       </c>
       <c r="Q245" s="2"/>
       <c r="R245" t="s" s="2">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="S245" t="s" s="2">
         <v>78</v>
@@ -31939,10 +31935,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -32002,7 +31998,7 @@
       </c>
       <c r="Y246" s="2"/>
       <c r="Z246" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="AA246" t="s" s="2">
         <v>78</v>
@@ -32052,10 +32048,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
+        <v>878</v>
+      </c>
+      <c r="B247" t="s" s="2">
         <v>879</v>
-      </c>
-      <c r="B247" t="s" s="2">
-        <v>880</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -32095,7 +32091,7 @@
       </c>
       <c r="Q247" s="2"/>
       <c r="R247" t="s" s="2">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="S247" t="s" s="2">
         <v>78</v>
@@ -32169,10 +32165,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
+        <v>881</v>
+      </c>
+      <c r="B248" t="s" s="2">
         <v>882</v>
-      </c>
-      <c r="B248" t="s" s="2">
-        <v>883</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -32284,14 +32280,14 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E249" s="2"/>
       <c r="F249" t="s" s="2">
@@ -32313,10 +32309,10 @@
         <v>111</v>
       </c>
       <c r="L249" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="M249" t="s" s="2">
         <v>817</v>
-      </c>
-      <c r="M249" t="s" s="2">
-        <v>818</v>
       </c>
       <c r="N249" t="s" s="2">
         <v>114</v>
@@ -32371,7 +32367,7 @@
         <v>78</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>79</v>
@@ -32403,10 +32399,10 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -32432,14 +32428,14 @@
         <v>362</v>
       </c>
       <c r="L250" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="M250" t="s" s="2">
         <v>821</v>
-      </c>
-      <c r="M250" t="s" s="2">
-        <v>822</v>
       </c>
       <c r="N250" s="2"/>
       <c r="O250" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="P250" t="s" s="2">
         <v>78</v>
@@ -32488,7 +32484,7 @@
         <v>78</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>79</v>
@@ -32509,7 +32505,7 @@
         <v>78</v>
       </c>
       <c r="AM250" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="AN250" t="s" s="2">
         <v>78</v>
@@ -32520,10 +32516,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -32549,10 +32545,10 @@
         <v>233</v>
       </c>
       <c r="L251" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="M251" t="s" s="2">
         <v>826</v>
-      </c>
-      <c r="M251" t="s" s="2">
-        <v>827</v>
       </c>
       <c r="N251" s="2"/>
       <c r="O251" s="2"/>
@@ -32583,7 +32579,7 @@
       </c>
       <c r="Y251" s="2"/>
       <c r="Z251" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="AA251" t="s" s="2">
         <v>78</v>
@@ -32601,7 +32597,7 @@
         <v>78</v>
       </c>
       <c r="AF251" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="AG251" t="s" s="2">
         <v>90</v>
@@ -32622,10 +32618,10 @@
         <v>78</v>
       </c>
       <c r="AM251" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="AN251" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="AO251" t="s" s="2">
         <v>78</v>
@@ -32633,10 +32629,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
+        <v>886</v>
+      </c>
+      <c r="B252" t="s" s="2">
         <v>887</v>
-      </c>
-      <c r="B252" t="s" s="2">
-        <v>888</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -32748,10 +32744,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
+        <v>888</v>
+      </c>
+      <c r="B253" t="s" s="2">
         <v>889</v>
-      </c>
-      <c r="B253" t="s" s="2">
-        <v>890</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -32865,10 +32861,10 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
+        <v>890</v>
+      </c>
+      <c r="B254" t="s" s="2">
         <v>891</v>
-      </c>
-      <c r="B254" t="s" s="2">
-        <v>892</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -32940,14 +32936,14 @@
         <v>78</v>
       </c>
       <c r="AB254" t="s" s="2">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="AC254" s="2"/>
       <c r="AD254" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE254" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AF254" t="s" s="2">
         <v>398</v>
@@ -32982,13 +32978,13 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
+        <v>893</v>
+      </c>
+      <c r="B255" t="s" s="2">
+        <v>891</v>
+      </c>
+      <c r="C255" t="s" s="2">
         <v>894</v>
-      </c>
-      <c r="B255" t="s" s="2">
-        <v>892</v>
-      </c>
-      <c r="C255" t="s" s="2">
-        <v>895</v>
       </c>
       <c r="D255" t="s" s="2">
         <v>78</v>
@@ -33051,7 +33047,7 @@
       </c>
       <c r="Y255" s="2"/>
       <c r="Z255" t="s" s="2">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="AA255" t="s" s="2">
         <v>78</v>
@@ -33101,13 +33097,13 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="D256" t="s" s="2">
         <v>78</v>
@@ -33170,7 +33166,7 @@
       </c>
       <c r="Y256" s="2"/>
       <c r="Z256" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="AA256" t="s" s="2">
         <v>78</v>
@@ -33220,10 +33216,10 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
+        <v>897</v>
+      </c>
+      <c r="B257" t="s" s="2">
         <v>898</v>
-      </c>
-      <c r="B257" t="s" s="2">
-        <v>899</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -33339,10 +33335,10 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -33368,14 +33364,14 @@
         <v>253</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="N258" s="2"/>
       <c r="O258" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="P258" t="s" s="2">
         <v>78</v>
@@ -33424,7 +33420,7 @@
         <v>78</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>79</v>
@@ -33445,10 +33441,10 @@
         <v>78</v>
       </c>
       <c r="AM258" t="s" s="2">
+        <v>833</v>
+      </c>
+      <c r="AN258" t="s" s="2">
         <v>834</v>
-      </c>
-      <c r="AN258" t="s" s="2">
-        <v>835</v>
       </c>
       <c r="AO258" t="s" s="2">
         <v>78</v>
@@ -33456,10 +33452,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
+        <v>901</v>
+      </c>
+      <c r="B259" t="s" s="2">
         <v>902</v>
-      </c>
-      <c r="B259" t="s" s="2">
-        <v>903</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -33571,10 +33567,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
+        <v>903</v>
+      </c>
+      <c r="B260" t="s" s="2">
         <v>904</v>
-      </c>
-      <c r="B260" t="s" s="2">
-        <v>905</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -33688,10 +33684,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
+        <v>905</v>
+      </c>
+      <c r="B261" t="s" s="2">
         <v>906</v>
-      </c>
-      <c r="B261" t="s" s="2">
-        <v>907</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -33717,7 +33713,7 @@
         <v>260</v>
       </c>
       <c r="L261" t="s" s="2">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="M261" t="s" s="2">
         <v>262</v>
@@ -33805,10 +33801,10 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
+        <v>908</v>
+      </c>
+      <c r="B262" t="s" s="2">
         <v>909</v>
-      </c>
-      <c r="B262" t="s" s="2">
-        <v>910</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -33834,7 +33830,7 @@
         <v>260</v>
       </c>
       <c r="L262" t="s" s="2">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="M262" t="s" s="2">
         <v>271</v>
@@ -33924,10 +33920,10 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -33950,13 +33946,13 @@
         <v>78</v>
       </c>
       <c r="K263" t="s" s="2">
+        <v>912</v>
+      </c>
+      <c r="L263" t="s" s="2">
         <v>913</v>
       </c>
-      <c r="L263" t="s" s="2">
-        <v>914</v>
-      </c>
       <c r="M263" t="s" s="2">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="N263" s="2"/>
       <c r="O263" s="2"/>
@@ -34007,7 +34003,7 @@
         <v>78</v>
       </c>
       <c r="AF263" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="AG263" t="s" s="2">
         <v>79</v>
@@ -34028,7 +34024,7 @@
         <v>78</v>
       </c>
       <c r="AM263" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="AN263" t="s" s="2">
         <v>78</v>
@@ -34039,13 +34035,13 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
+        <v>914</v>
+      </c>
+      <c r="B264" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="C264" t="s" s="2">
         <v>915</v>
-      </c>
-      <c r="B264" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="C264" t="s" s="2">
-        <v>916</v>
       </c>
       <c r="D264" t="s" s="2">
         <v>78</v>
@@ -34067,13 +34063,13 @@
         <v>78</v>
       </c>
       <c r="K264" t="s" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="L264" t="s" s="2">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="M264" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="N264" s="2"/>
       <c r="O264" s="2"/>
@@ -34124,7 +34120,7 @@
         <v>78</v>
       </c>
       <c r="AF264" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="AG264" t="s" s="2">
         <v>79</v>
@@ -34142,13 +34138,13 @@
         <v>78</v>
       </c>
       <c r="AL264" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="AM264" t="s" s="2">
         <v>810</v>
       </c>
-      <c r="AM264" t="s" s="2">
+      <c r="AN264" t="s" s="2">
         <v>811</v>
-      </c>
-      <c r="AN264" t="s" s="2">
-        <v>812</v>
       </c>
       <c r="AO264" t="s" s="2">
         <v>78</v>
@@ -34156,10 +34152,10 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -34271,10 +34267,10 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -34388,14 +34384,14 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E267" s="2"/>
       <c r="F267" t="s" s="2">
@@ -34417,10 +34413,10 @@
         <v>111</v>
       </c>
       <c r="L267" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="M267" t="s" s="2">
         <v>817</v>
-      </c>
-      <c r="M267" t="s" s="2">
-        <v>818</v>
       </c>
       <c r="N267" t="s" s="2">
         <v>114</v>
@@ -34475,7 +34471,7 @@
         <v>78</v>
       </c>
       <c r="AF267" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="AG267" t="s" s="2">
         <v>79</v>
@@ -34507,10 +34503,10 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -34536,14 +34532,14 @@
         <v>362</v>
       </c>
       <c r="L268" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="M268" t="s" s="2">
         <v>821</v>
-      </c>
-      <c r="M268" t="s" s="2">
-        <v>822</v>
       </c>
       <c r="N268" s="2"/>
       <c r="O268" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="P268" t="s" s="2">
         <v>78</v>
@@ -34592,7 +34588,7 @@
         <v>78</v>
       </c>
       <c r="AF268" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="AG268" t="s" s="2">
         <v>79</v>
@@ -34613,7 +34609,7 @@
         <v>78</v>
       </c>
       <c r="AM268" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="AN268" t="s" s="2">
         <v>78</v>
@@ -34624,10 +34620,10 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -34653,10 +34649,10 @@
         <v>233</v>
       </c>
       <c r="L269" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="M269" t="s" s="2">
         <v>826</v>
-      </c>
-      <c r="M269" t="s" s="2">
-        <v>827</v>
       </c>
       <c r="N269" s="2"/>
       <c r="O269" s="2"/>
@@ -34687,7 +34683,7 @@
       </c>
       <c r="Y269" s="2"/>
       <c r="Z269" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="AA269" t="s" s="2">
         <v>78</v>
@@ -34705,7 +34701,7 @@
         <v>78</v>
       </c>
       <c r="AF269" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="AG269" t="s" s="2">
         <v>90</v>
@@ -34726,10 +34722,10 @@
         <v>78</v>
       </c>
       <c r="AM269" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="AN269" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="AO269" t="s" s="2">
         <v>78</v>
@@ -34737,10 +34733,10 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -34852,10 +34848,10 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -34969,10 +34965,10 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
@@ -35044,14 +35040,14 @@
         <v>78</v>
       </c>
       <c r="AB272" t="s" s="2">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="AC272" s="2"/>
       <c r="AD272" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE272" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AF272" t="s" s="2">
         <v>398</v>
@@ -35086,13 +35082,13 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
+        <v>925</v>
+      </c>
+      <c r="B273" t="s" s="2">
+        <v>891</v>
+      </c>
+      <c r="C273" t="s" s="2">
         <v>926</v>
-      </c>
-      <c r="B273" t="s" s="2">
-        <v>892</v>
-      </c>
-      <c r="C273" t="s" s="2">
-        <v>927</v>
       </c>
       <c r="D273" t="s" s="2">
         <v>78</v>
@@ -35117,7 +35113,7 @@
         <v>154</v>
       </c>
       <c r="L273" t="s" s="2">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="M273" t="s" s="2">
         <v>395</v>
@@ -35155,7 +35151,7 @@
       </c>
       <c r="Y273" s="2"/>
       <c r="Z273" t="s" s="2">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="AA273" t="s" s="2">
         <v>78</v>
@@ -35205,10 +35201,10 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C274" t="s" s="2">
         <v>337</v>
@@ -35236,7 +35232,7 @@
         <v>154</v>
       </c>
       <c r="L274" t="s" s="2">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="M274" t="s" s="2">
         <v>395</v>
@@ -35324,10 +35320,10 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
@@ -35443,10 +35439,10 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -35472,14 +35468,14 @@
         <v>253</v>
       </c>
       <c r="L276" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="M276" t="s" s="2">
         <v>831</v>
-      </c>
-      <c r="M276" t="s" s="2">
-        <v>832</v>
       </c>
       <c r="N276" s="2"/>
       <c r="O276" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="P276" t="s" s="2">
         <v>78</v>
@@ -35528,7 +35524,7 @@
         <v>78</v>
       </c>
       <c r="AF276" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="AG276" t="s" s="2">
         <v>79</v>
@@ -35549,10 +35545,10 @@
         <v>78</v>
       </c>
       <c r="AM276" t="s" s="2">
+        <v>833</v>
+      </c>
+      <c r="AN276" t="s" s="2">
         <v>834</v>
-      </c>
-      <c r="AN276" t="s" s="2">
-        <v>835</v>
       </c>
       <c r="AO276" t="s" s="2">
         <v>78</v>
@@ -35560,10 +35556,10 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -35675,10 +35671,10 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -35792,10 +35788,10 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -35821,7 +35817,7 @@
         <v>260</v>
       </c>
       <c r="L279" t="s" s="2">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="M279" t="s" s="2">
         <v>262</v>
@@ -35909,10 +35905,10 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -35938,7 +35934,7 @@
         <v>260</v>
       </c>
       <c r="L280" t="s" s="2">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="M280" t="s" s="2">
         <v>271</v>
@@ -36028,10 +36024,10 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
@@ -36057,10 +36053,10 @@
         <v>476</v>
       </c>
       <c r="L281" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="M281" t="s" s="2">
         <v>837</v>
-      </c>
-      <c r="M281" t="s" s="2">
-        <v>838</v>
       </c>
       <c r="N281" s="2"/>
       <c r="O281" s="2"/>
@@ -36111,7 +36107,7 @@
         <v>78</v>
       </c>
       <c r="AF281" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="AG281" t="s" s="2">
         <v>79</v>
@@ -36132,7 +36128,7 @@
         <v>78</v>
       </c>
       <c r="AM281" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="AN281" t="s" s="2">
         <v>78</v>
@@ -36143,13 +36139,13 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
+        <v>940</v>
+      </c>
+      <c r="B282" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="C282" t="s" s="2">
         <v>941</v>
-      </c>
-      <c r="B282" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="C282" t="s" s="2">
-        <v>942</v>
       </c>
       <c r="D282" t="s" s="2">
         <v>78</v>
@@ -36171,13 +36167,13 @@
         <v>78</v>
       </c>
       <c r="K282" t="s" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="L282" t="s" s="2">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="M282" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="N282" s="2"/>
       <c r="O282" s="2"/>
@@ -36228,7 +36224,7 @@
         <v>78</v>
       </c>
       <c r="AF282" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="AG282" t="s" s="2">
         <v>79</v>
@@ -36246,13 +36242,13 @@
         <v>78</v>
       </c>
       <c r="AL282" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="AM282" t="s" s="2">
         <v>810</v>
       </c>
-      <c r="AM282" t="s" s="2">
+      <c r="AN282" t="s" s="2">
         <v>811</v>
-      </c>
-      <c r="AN282" t="s" s="2">
-        <v>812</v>
       </c>
       <c r="AO282" t="s" s="2">
         <v>78</v>
@@ -36260,10 +36256,10 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -36375,10 +36371,10 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
@@ -36492,14 +36488,14 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E285" s="2"/>
       <c r="F285" t="s" s="2">
@@ -36521,10 +36517,10 @@
         <v>111</v>
       </c>
       <c r="L285" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="M285" t="s" s="2">
         <v>817</v>
-      </c>
-      <c r="M285" t="s" s="2">
-        <v>818</v>
       </c>
       <c r="N285" t="s" s="2">
         <v>114</v>
@@ -36579,7 +36575,7 @@
         <v>78</v>
       </c>
       <c r="AF285" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="AG285" t="s" s="2">
         <v>79</v>
@@ -36611,10 +36607,10 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
@@ -36640,14 +36636,14 @@
         <v>362</v>
       </c>
       <c r="L286" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="M286" t="s" s="2">
         <v>821</v>
-      </c>
-      <c r="M286" t="s" s="2">
-        <v>822</v>
       </c>
       <c r="N286" s="2"/>
       <c r="O286" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="P286" t="s" s="2">
         <v>78</v>
@@ -36696,7 +36692,7 @@
         <v>78</v>
       </c>
       <c r="AF286" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="AG286" t="s" s="2">
         <v>79</v>
@@ -36717,7 +36713,7 @@
         <v>78</v>
       </c>
       <c r="AM286" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="AN286" t="s" s="2">
         <v>78</v>
@@ -36728,10 +36724,10 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
@@ -36757,10 +36753,10 @@
         <v>233</v>
       </c>
       <c r="L287" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="M287" t="s" s="2">
         <v>826</v>
-      </c>
-      <c r="M287" t="s" s="2">
-        <v>827</v>
       </c>
       <c r="N287" s="2"/>
       <c r="O287" s="2"/>
@@ -36791,7 +36787,7 @@
       </c>
       <c r="Y287" s="2"/>
       <c r="Z287" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="AA287" t="s" s="2">
         <v>78</v>
@@ -36809,7 +36805,7 @@
         <v>78</v>
       </c>
       <c r="AF287" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="AG287" t="s" s="2">
         <v>90</v>
@@ -36824,16 +36820,16 @@
         <v>102</v>
       </c>
       <c r="AK287" t="s" s="2">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="AL287" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM287" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="AN287" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="AO287" t="s" s="2">
         <v>78</v>
@@ -36841,10 +36837,10 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
@@ -36956,10 +36952,10 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" t="s" s="2">
@@ -37073,10 +37069,10 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
@@ -37148,7 +37144,7 @@
         <v>78</v>
       </c>
       <c r="AB290" t="s" s="2">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="AC290" s="2"/>
       <c r="AD290" t="s" s="2">
@@ -37190,13 +37186,13 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="D291" t="s" s="2">
         <v>78</v>
@@ -37221,7 +37217,7 @@
         <v>154</v>
       </c>
       <c r="L291" t="s" s="2">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="M291" t="s" s="2">
         <v>395</v>
@@ -37259,7 +37255,7 @@
       </c>
       <c r="Y291" s="2"/>
       <c r="Z291" t="s" s="2">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="AA291" t="s" s="2">
         <v>78</v>
@@ -37309,13 +37305,13 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="D292" t="s" s="2">
         <v>78</v>
@@ -37340,7 +37336,7 @@
         <v>154</v>
       </c>
       <c r="L292" t="s" s="2">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="M292" t="s" s="2">
         <v>395</v>
@@ -37378,7 +37374,7 @@
       </c>
       <c r="Y292" s="2"/>
       <c r="Z292" t="s" s="2">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="AA292" t="s" s="2">
         <v>78</v>
@@ -37428,10 +37424,10 @@
     </row>
     <row r="293" hidden="true">
       <c r="A293" t="s" s="2">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C293" s="2"/>
       <c r="D293" t="s" s="2">
@@ -37547,10 +37543,10 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C294" s="2"/>
       <c r="D294" t="s" s="2">
@@ -37576,14 +37572,14 @@
         <v>253</v>
       </c>
       <c r="L294" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="M294" t="s" s="2">
         <v>831</v>
-      </c>
-      <c r="M294" t="s" s="2">
-        <v>832</v>
       </c>
       <c r="N294" s="2"/>
       <c r="O294" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="P294" t="s" s="2">
         <v>78</v>
@@ -37632,7 +37628,7 @@
         <v>78</v>
       </c>
       <c r="AF294" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="AG294" t="s" s="2">
         <v>79</v>
@@ -37653,10 +37649,10 @@
         <v>78</v>
       </c>
       <c r="AM294" t="s" s="2">
+        <v>833</v>
+      </c>
+      <c r="AN294" t="s" s="2">
         <v>834</v>
-      </c>
-      <c r="AN294" t="s" s="2">
-        <v>835</v>
       </c>
       <c r="AO294" t="s" s="2">
         <v>78</v>
@@ -37664,10 +37660,10 @@
     </row>
     <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" t="s" s="2">
@@ -37779,10 +37775,10 @@
     </row>
     <row r="296" hidden="true">
       <c r="A296" t="s" s="2">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C296" s="2"/>
       <c r="D296" t="s" s="2">
@@ -37896,10 +37892,10 @@
     </row>
     <row r="297" hidden="true">
       <c r="A297" t="s" s="2">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C297" s="2"/>
       <c r="D297" t="s" s="2">
@@ -37925,7 +37921,7 @@
         <v>260</v>
       </c>
       <c r="L297" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="M297" t="s" s="2">
         <v>262</v>
@@ -37996,7 +37992,7 @@
         <v>102</v>
       </c>
       <c r="AK297" t="s" s="2">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="AL297" t="s" s="2">
         <v>266</v>
@@ -38013,10 +38009,10 @@
     </row>
     <row r="298" hidden="true">
       <c r="A298" t="s" s="2">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C298" s="2"/>
       <c r="D298" t="s" s="2">
@@ -38042,7 +38038,7 @@
         <v>260</v>
       </c>
       <c r="L298" t="s" s="2">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="M298" t="s" s="2">
         <v>271</v>
@@ -38115,7 +38111,7 @@
         <v>102</v>
       </c>
       <c r="AK298" t="s" s="2">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="AL298" t="s" s="2">
         <v>275</v>
@@ -38132,10 +38128,10 @@
     </row>
     <row r="299" hidden="true">
       <c r="A299" t="s" s="2">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C299" s="2"/>
       <c r="D299" t="s" s="2">
@@ -38161,10 +38157,10 @@
         <v>476</v>
       </c>
       <c r="L299" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="M299" t="s" s="2">
         <v>837</v>
-      </c>
-      <c r="M299" t="s" s="2">
-        <v>838</v>
       </c>
       <c r="N299" s="2"/>
       <c r="O299" s="2"/>
@@ -38215,7 +38211,7 @@
         <v>78</v>
       </c>
       <c r="AF299" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="AG299" t="s" s="2">
         <v>79</v>
@@ -38236,7 +38232,7 @@
         <v>78</v>
       </c>
       <c r="AM299" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="AN299" t="s" s="2">
         <v>78</v>
@@ -38247,10 +38243,10 @@
     </row>
     <row r="300" hidden="true">
       <c r="A300" t="s" s="2">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="C300" s="2"/>
       <c r="D300" t="s" s="2">
@@ -38273,19 +38269,19 @@
         <v>78</v>
       </c>
       <c r="K300" t="s" s="2">
+        <v>970</v>
+      </c>
+      <c r="L300" t="s" s="2">
         <v>971</v>
       </c>
-      <c r="L300" t="s" s="2">
+      <c r="M300" t="s" s="2">
         <v>972</v>
       </c>
-      <c r="M300" t="s" s="2">
+      <c r="N300" t="s" s="2">
         <v>973</v>
       </c>
-      <c r="N300" t="s" s="2">
+      <c r="O300" t="s" s="2">
         <v>974</v>
-      </c>
-      <c r="O300" t="s" s="2">
-        <v>975</v>
       </c>
       <c r="P300" t="s" s="2">
         <v>78</v>
@@ -38314,7 +38310,7 @@
       </c>
       <c r="Y300" s="2"/>
       <c r="Z300" t="s" s="2">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="AA300" t="s" s="2">
         <v>78</v>
@@ -38332,7 +38328,7 @@
         <v>78</v>
       </c>
       <c r="AF300" t="s" s="2">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="AG300" t="s" s="2">
         <v>79</v>
@@ -38350,10 +38346,10 @@
         <v>78</v>
       </c>
       <c r="AL300" t="s" s="2">
+        <v>976</v>
+      </c>
+      <c r="AM300" t="s" s="2">
         <v>977</v>
-      </c>
-      <c r="AM300" t="s" s="2">
-        <v>978</v>
       </c>
       <c r="AN300" t="s" s="2">
         <v>78</v>
